--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB71C074-186B-4A80-8810-85F63CA355CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E7051F-4ECF-49A7-BBCA-1E85DB8BA891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 19-12-2025'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 29-01-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E7051F-4ECF-49A7-BBCA-1E85DB8BA891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40640A8-D368-40F9-A365-D092BDDF570D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 29-01-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-02-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40640A8-D368-40F9-A365-D092BDDF570D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F10E47-971E-42D8-88FA-542C9BF6E5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-02-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 20-02-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -587,9 +587,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -656,7 +656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -723,7 +723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -758,7 +758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -793,7 +793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -807,7 +807,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -839,7 +839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -874,7 +874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -906,7 +906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -941,7 +941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -970,7 +970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F10E47-971E-42D8-88FA-542C9BF6E5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139F8C7D-89D4-4C96-9645-8329F89B6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 20-02-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 04-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139F8C7D-89D4-4C96-9645-8329F89B6E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D79A2-8D6E-4353-943A-5A22EC862F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 04-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D79A2-8D6E-4353-943A-5A22EC862F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F46F7CE-7000-4825-B626-8E85AAC43DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F46F7CE-7000-4825-B626-8E85AAC43DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C1D5A3-CF9C-41B9-9602-4A7679884313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C1D5A3-CF9C-41B9-9602-4A7679884313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFFB3BA-7F6F-456C-B769-5C9C7A0D82CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFFB3BA-7F6F-456C-B769-5C9C7A0D82CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459E14A6-8C7C-4242-9D19-0C8A93EC0583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459E14A6-8C7C-4242-9D19-0C8A93EC0583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF7D108-C23F-4354-A10A-15E9C220E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF7D108-C23F-4354-A10A-15E9C220E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38221177-E474-4688-ACBE-6BE1EB87C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38221177-E474-4688-ACBE-6BE1EB87C60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2563C866-BDB3-4417-A511-54CF7A55569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 11-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 20-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2563C866-BDB3-4417-A511-54CF7A55569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B0E4E6-4478-4B34-B973-7A6E936366F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 20-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 25-03-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B0E4E6-4478-4B34-B973-7A6E936366F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC2FBA-A50B-41B5-BFA5-101B2BF0FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 25-03-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 08-04-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC2FBA-A50B-41B5-BFA5-101B2BF0FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D6CF11-4652-440F-956E-9CE3F5AC4380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 08-04-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 10-04-2026'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D6CF11-4652-440F-956E-9CE3F5AC4380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC1636D-F494-4DC7-A5E7-14E660C81A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC1636D-F494-4DC7-A5E7-14E660C81A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A70CA-2A45-4E3A-A123-65167D9EE7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 10-04-2026'!$A$1:$K$35</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 14-04-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
   <si>
     <t>Standard</t>
   </si>
@@ -215,6 +215,39 @@
   </si>
   <si>
     <t>RPT04 (R0432P)</t>
+  </si>
+  <si>
+    <t>DischargeLetter</t>
+  </si>
+  <si>
+    <t>XDIS01 (XD0134L)</t>
+  </si>
+  <si>
+    <t>OutPatientDischargeLetter</t>
+  </si>
+  <si>
+    <t>XDIS02 (XD0234L)</t>
+  </si>
+  <si>
+    <t>CasualtyWardLetter</t>
+  </si>
+  <si>
+    <t>XDIS03 (XD0334L)</t>
+  </si>
+  <si>
+    <t>Emergencyletter</t>
+  </si>
+  <si>
+    <t>XDIS06 (XD0633L)</t>
+  </si>
+  <si>
+    <t>PrivateSpecialistLetter</t>
+  </si>
+  <si>
+    <t>XDIS07 (XD0733L)</t>
+  </si>
+  <si>
+    <t>XDIS07 (XD0734L)</t>
   </si>
   <si>
     <t>PhysiotherapiLetter</t>
@@ -586,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -935,7 +968,7 @@
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
@@ -996,7 +1029,7 @@
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K13" t="s">
         <v>14</v>
@@ -1063,7 +1096,7 @@
         <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
         <v>14</v>
@@ -1098,7 +1131,7 @@
         <v>14</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K16" t="s">
         <v>14</v>
@@ -1133,7 +1166,7 @@
         <v>14</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K17" t="s">
         <v>14</v>
@@ -1168,7 +1201,7 @@
         <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K18" t="s">
         <v>14</v>
@@ -1592,8 +1625,8 @@
       <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="E31" t="s">
-        <v>14</v>
+      <c r="J31" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -1606,8 +1639,8 @@
       <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="E32" t="s">
-        <v>14</v>
+      <c r="J32" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -1620,11 +1653,8 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="E33" t="s">
-        <v>14</v>
-      </c>
       <c r="J33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -1637,11 +1667,8 @@
       <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="E34" t="s">
-        <v>14</v>
-      </c>
       <c r="J34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -1654,28 +1681,121 @@
       <c r="C35" t="s">
         <v>13</v>
       </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" t="s">
-        <v>14</v>
-      </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
-      <c r="K35" t="s">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A70CA-2A45-4E3A-A123-65167D9EE7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829243E-351E-4115-974E-5268A77144F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 14-04-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 24-04-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829243E-351E-4115-974E-5268A77144F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4F1391-DAB2-4678-8B54-627EBA3E6A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4F1391-DAB2-4678-8B54-627EBA3E6A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF572A4-2942-4726-8CFC-7A0632177337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 24-04-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 27-04-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF572A4-2942-4726-8CFC-7A0632177337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D206CE-1CFB-4C0F-A69F-D3B11F24B581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 27-04-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-05-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D206CE-1CFB-4C0F-A69F-D3B11F24B581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5EA8D-8398-49BE-BB30-AAE56F6E799E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-05-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 01-06-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E5EA8D-8398-49BE-BB30-AAE56F6E799E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A269701E-DC21-48F4-A8A9-0A06980756D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 01-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-06-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A269701E-DC21-48F4-A8A9-0A06980756D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95199350-05C3-4897-B6FE-E5A22AE91624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95199350-05C3-4897-B6FE-E5A22AE91624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9762E022-8DA2-43A2-8A32-0029A587C62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 05-06-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E7051F-4ECF-49A7-BBCA-1E85DB8BA891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8EC21C-A7EE-485F-820B-7A65E94A074B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6AC715-F83A-4E58-8606-91370F1A7FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E69E87-F61A-407B-B2B9-C4BBD21EDFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E69E87-F61A-407B-B2B9-C4BBD21EDFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4F68E0-8FD6-4603-855E-713670C9DAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4F68E0-8FD6-4603-855E-713670C9DAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FAE12-C468-48EE-B341-92EA5201CA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 15-06-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -620,9 +620,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -657,7 +657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -689,7 +689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -721,7 +721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -756,7 +756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -791,7 +791,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -840,7 +840,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -872,7 +872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -939,7 +939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -974,7 +974,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1671,7 +1671,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FAE12-C468-48EE-B341-92EA5201CA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58D2855-75E3-42FC-8BDA-F9166C45E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 15-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58D2855-75E3-42FC-8BDA-F9166C45E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3421D5E7-9033-458A-B815-D9721ED0324B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$K$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="87">
   <si>
     <t>Standard</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>XREF02 (XH0231R)</t>
+  </si>
+  <si>
+    <t>CervixcytologyReport</t>
+  </si>
+  <si>
+    <t>XRPT03 (XR0331P)</t>
   </si>
   <si>
     <t>MicrobiologyWebReport</t>
@@ -619,10 +625,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -657,7 +663,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -689,7 +695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -721,7 +727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -756,7 +762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -791,7 +797,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -826,7 +832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -840,7 +846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -872,7 +878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -907,7 +913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -939,7 +945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -974,7 +980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1035,7 +1041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1070,7 +1076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1137,7 +1143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1207,7 +1213,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1277,7 +1283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1379,7 +1385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1414,7 +1420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1481,7 +1487,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1513,7 +1519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>58</v>
       </c>
@@ -1542,13 +1548,13 @@
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1609,13 +1615,13 @@
         <v>14</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -1629,7 +1635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1643,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>68</v>
       </c>
@@ -1657,7 +1663,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1671,7 +1677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1685,7 +1691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1699,7 +1705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1716,7 +1722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1730,7 +1736,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1747,7 +1753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1774,28 +1780,42 @@
       <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
       <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3421D5E7-9033-458A-B815-D9721ED0324B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3818039-7EED-4918-9060-4752DFB65AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$K$42</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$K$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="89">
   <si>
     <t>Standard</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>XRPT03 (XR0331P)</t>
+  </si>
+  <si>
+    <t>HistopathologyReport</t>
+  </si>
+  <si>
+    <t>XRPT04 (XR0431P)</t>
   </si>
   <si>
     <t>MicrobiologyWebReport</t>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1794,28 +1800,42 @@
       <c r="C42" t="s">
         <v>13</v>
       </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I42" t="s">
-        <v>14</v>
-      </c>
       <c r="J42" t="s">
         <v>14</v>
       </c>
-      <c r="K42" t="s">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58D2855-75E3-42FC-8BDA-F9166C45E060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E12380-1A4B-486C-97ED-FDAC2EA276B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 22-06-2026'!$A$1:$K$41</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$K$43</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="89">
   <si>
     <t>Standard</t>
   </si>
@@ -272,6 +272,18 @@
   </si>
   <si>
     <t>XREF02 (XH0231R)</t>
+  </si>
+  <si>
+    <t>CervixcytologyReport</t>
+  </si>
+  <si>
+    <t>XRPT03 (XR0331P)</t>
+  </si>
+  <si>
+    <t>HistopathologyReport</t>
+  </si>
+  <si>
+    <t>XRPT04 (XR0431P)</t>
   </si>
   <si>
     <t>MicrobiologyWebReport</t>
@@ -619,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -1542,7 +1554,7 @@
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K28" t="s">
         <v>14</v>
@@ -1609,7 +1621,7 @@
         <v>14</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s">
         <v>14</v>
@@ -1774,28 +1786,56 @@
       <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" t="s">
-        <v>17</v>
-      </c>
-      <c r="G41" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" t="s">
-        <v>14</v>
-      </c>
       <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" t="s">
         <v>14</v>
       </c>
     </row>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E12380-1A4B-486C-97ED-FDAC2EA276B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F58001D-4D8F-4594-A0FE-FF2CBFA4D62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 23-06-2026'!$A$1:$K$43</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 25-06-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="110">
   <si>
     <t>Standard</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Clinea _Privath__ (EG)</t>
   </si>
   <si>
+    <t>Clinio _Privath__ (Clinio Medical)</t>
+  </si>
+  <si>
     <t>EPM _Privath__ (Metodika)</t>
   </si>
   <si>
@@ -169,6 +172,12 @@
     <t>DIS91 (D9134L)</t>
   </si>
   <si>
+    <t>RehabilitationPlan</t>
+  </si>
+  <si>
+    <t>GGOP (GGOP100)</t>
+  </si>
+  <si>
     <t>Sygehushenvisning</t>
   </si>
   <si>
@@ -181,6 +190,12 @@
     <t>REF02 (H0231R)</t>
   </si>
   <si>
+    <t>Speciallægehenvisning</t>
+  </si>
+  <si>
+    <t>REF06 (H0631R)</t>
+  </si>
+  <si>
     <t>Laboratoriesvar</t>
   </si>
   <si>
@@ -217,6 +232,36 @@
     <t>RPT04 (R0432P)</t>
   </si>
   <si>
+    <t>Den gode VANSEnvelope</t>
+  </si>
+  <si>
+    <t>VANSEnvelope (1.0)</t>
+  </si>
+  <si>
+    <t>BinaryLetter</t>
+  </si>
+  <si>
+    <t>XBIN01 (XB0131X)</t>
+  </si>
+  <si>
+    <t>NegativeVansReceipt</t>
+  </si>
+  <si>
+    <t>XCTL01 (XC0130Q)</t>
+  </si>
+  <si>
+    <t>NegativeReceipt</t>
+  </si>
+  <si>
+    <t>XCTL02 (XC0230Q)</t>
+  </si>
+  <si>
+    <t>PositiveReceipt</t>
+  </si>
+  <si>
+    <t>XCTL03 (XC0330Q)</t>
+  </si>
+  <si>
     <t>DischargeLetter</t>
   </si>
   <si>
@@ -235,6 +280,12 @@
     <t>XDIS03 (XD0334L)</t>
   </si>
   <si>
+    <t>RadiologyReport</t>
+  </si>
+  <si>
+    <t>XDIS05 (XD0533L)</t>
+  </si>
+  <si>
     <t>Emergencyletter</t>
   </si>
   <si>
@@ -262,6 +313,12 @@
     <t>XDIS13 (XD1333L)</t>
   </si>
   <si>
+    <t>ReportOfAdmission</t>
+  </si>
+  <si>
+    <t>XDIS16 (XD1634C)</t>
+  </si>
+  <si>
     <t>HospitalReferral</t>
   </si>
   <si>
@@ -272,6 +329,12 @@
   </si>
   <si>
     <t>XREF02 (XH0231R)</t>
+  </si>
+  <si>
+    <t>PrivateSpecialistReferral</t>
+  </si>
+  <si>
+    <t>XREF06 (XH0631R)</t>
   </si>
   <si>
     <t>CervixcytologyReport</t>
@@ -631,10 +694,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -668,1175 +731,1363 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="L28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
       </c>
       <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="K38" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="K39" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="K40" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="J41" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="K42" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43" t="s">
         <v>14</v>
       </c>
       <c r="K43" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>15</v>
+      </c>
+      <c r="L53" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F58001D-4D8F-4594-A0FE-FF2CBFA4D62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7251068F-46C2-406F-A963-399F8FC503D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 25-06-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 30-06-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7251068F-46C2-406F-A963-399F8FC503D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E120E1CA-3467-4B73-AA34-CC972F61C4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E120E1CA-3467-4B73-AA34-CC972F61C4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02D961-E3DA-4F29-8B86-4C85D8AB78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 30-06-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02D961-E3DA-4F29-8B86-4C85D8AB78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C17613-CB67-4A4A-A5A8-DC130D9EF1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-07-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C02D961-E3DA-4F29-8B86-4C85D8AB78ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF51B7F2-49BC-49E8-BD53-057490FE52FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 01-07-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C17613-CB67-4A4A-A5A8-DC130D9EF1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1CD0EA-61B9-431C-9036-C423F402DEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-07-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1CD0EA-61B9-431C-9036-C423F402DEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3C0A7C-DFB4-438C-BFCE-04C6A7C2DF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 03-07-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-07-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3C0A7C-DFB4-438C-BFCE-04C6A7C2DF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71891A62-9C76-4614-9F3A-61D9164D9ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-07-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 19-08-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71891A62-9C76-4614-9F3A-61D9164D9ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC23D4-4AAC-45A3-862F-92C9B44BA1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 19-08-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 21-08-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADC23D4-4AAC-45A3-862F-92C9B44BA1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9396C769-5E8F-4F55-9683-E2941BC5314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 21-08-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 27-08-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -695,9 +695,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -767,7 +767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -878,7 +878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -916,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -962,7 +962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>71</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>96</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>98</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>100</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>108</v>
       </c>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9396C769-5E8F-4F55-9683-E2941BC5314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2512632E-A7F0-4D61-934C-1CF449E34BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 27-08-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2512632E-A7F0-4D61-934C-1CF449E34BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1B9FA1-69EF-4F22-9CA9-ED0046C323C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 02-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1B9FA1-69EF-4F22-9CA9-ED0046C323C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D3C56B-D0BB-47A5-A136-458710569CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D3C56B-D0BB-47A5-A136-458710569CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFE6BF6-F0EA-4D7D-BA0F-5638C591BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 06-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 07-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFE6BF6-F0EA-4D7D-BA0F-5638C591BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2E254C-75F0-486E-AF7E-9167D2744DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 07-09-2026'!$A$1:$L$53</definedName>
+    <definedName name="Privathospitalssystemer___modtage">'Opdateret d. 09-09-2026'!$A$1:$L$53</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - modtage_excel.XLSX
+++ b/html/Privathospitalssystemer - modtage_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2E254C-75F0-486E-AF7E-9167D2744DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908C4127-C248-4318-8EA6-928D84CFC88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
